--- a/tool/PMP/file/table/PaperGraphs.xlsx
+++ b/tool/PMP/file/table/PaperGraphs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\PMP\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9187C408-D60C-46CA-B7B3-F186C66F1087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED004CF-6325-422E-97B0-72AE74D6FB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{610F9EBE-991A-4E48-A0B8-267B2DA93B21}"/>
   </bookViews>
@@ -977,7 +977,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
